--- a/Project/outputs/tables/table_lstm_metrics_h22.xlsx
+++ b/Project/outputs/tables/table_lstm_metrics_h22.xlsx
@@ -482,19 +482,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02696932479739189</v>
+        <v>0.02587754838168621</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08357837796211243</v>
+        <v>0.07793319225311279</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1642233990556519</v>
+        <v>0.1608650004870115</v>
       </c>
       <c r="E2" t="n">
-        <v>49.26145935058594</v>
+        <v>41.19044876098633</v>
       </c>
       <c r="F2" t="n">
-        <v>0.461839530332681</v>
+        <v>0.4573055028462998</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -513,23 +513,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01311122626066208</v>
+        <v>0.01619019918143749</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06753960251808167</v>
+        <v>0.08014041185379028</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1145042630676346</v>
+        <v>0.1272407135371281</v>
       </c>
       <c r="E3" t="n">
-        <v>47.60640716552734</v>
+        <v>45.14357757568359</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5088062622309197</v>
+        <v>0.4952561669829222</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -548,23 +548,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01286481786519289</v>
+        <v>0.0167197585105896</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06152652204036713</v>
+        <v>0.0820842981338501</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1134231804579332</v>
+        <v>0.1293049052069936</v>
       </c>
       <c r="E4" t="n">
-        <v>33.9433479309082</v>
+        <v>48.46355056762695</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5088062622309197</v>
+        <v>0.5009487666034156</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -583,23 +583,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0155556034296751</v>
+        <v>0.01205893792212009</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0775822252035141</v>
+        <v>0.05889899656176567</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1247221048157667</v>
+        <v>0.1098131955737565</v>
       </c>
       <c r="E5" t="n">
-        <v>46.93355560302734</v>
+        <v>31.09530830383301</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5088062622309197</v>
+        <v>0.4952561669829222</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.006493748165667057</v>
+        <v>0.006246909033507109</v>
       </c>
       <c r="C6" t="n">
-        <v>0.05822910740971565</v>
+        <v>0.04896858707070351</v>
       </c>
       <c r="D6" t="n">
-        <v>0.080583795924907</v>
+        <v>0.07903739009802328</v>
       </c>
       <c r="E6" t="n">
-        <v>32.71009826660156</v>
+        <v>25.48544120788574</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4892367906066536</v>
+        <v>0.4971537001897533</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -653,23 +653,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.005554920062422752</v>
+        <v>0.01115692965686321</v>
       </c>
       <c r="C7" t="n">
-        <v>0.05358833074569702</v>
+        <v>0.05768842250108719</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07453133611054315</v>
+        <v>0.1056263681893078</v>
       </c>
       <c r="E7" t="n">
-        <v>26.82683181762695</v>
+        <v>26.84249877929688</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4814090019569471</v>
+        <v>0.5028462998102466</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -688,23 +688,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02294305339455605</v>
+        <v>0.004812152590602636</v>
       </c>
       <c r="C8" t="n">
-        <v>0.09509742259979248</v>
+        <v>0.047821044921875</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1514696451258669</v>
+        <v>0.06936968062923914</v>
       </c>
       <c r="E8" t="n">
-        <v>45.66630172729492</v>
+        <v>22.36306190490723</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4579256360078278</v>
+        <v>0.4933586337760911</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -723,23 +723,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.005413503386080265</v>
+        <v>0.006051102187484503</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05874574184417725</v>
+        <v>0.06723308563232422</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07357651382119341</v>
+        <v>0.07778883073735267</v>
       </c>
       <c r="E9" t="n">
-        <v>34.45508193969727</v>
+        <v>49.24911880493164</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5048923679060665</v>
+        <v>0.4857685009487666</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01361327467020601</v>
+        <v>0.01238919218303636</v>
       </c>
       <c r="C10" t="n">
-        <v>0.06948591629043221</v>
+        <v>0.06509600486606359</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1121292797974371</v>
+        <v>0.1073807605573516</v>
       </c>
       <c r="E10" t="n">
-        <v>39.67538452148438</v>
+        <v>36.2291259765625</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4902152641878669</v>
+        <v>0.4909867172675522</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.004743196070194244</v>
+        <v>0.005887490697205067</v>
       </c>
       <c r="C11" t="n">
-        <v>0.04417923837900162</v>
+        <v>0.04749452695250511</v>
       </c>
       <c r="D11" t="n">
-        <v>0.06887086517675123</v>
+        <v>0.07672998564580256</v>
       </c>
       <c r="E11" t="n">
-        <v>28.48289108276367</v>
+        <v>25.56708145141602</v>
       </c>
       <c r="F11" t="n">
-        <v>0.478796169630643</v>
+        <v>0.5026881720430108</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -828,23 +828,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.003843114711344242</v>
+        <v>0.003978682681918144</v>
       </c>
       <c r="C12" t="n">
-        <v>0.04835175722837448</v>
+        <v>0.05198376625776291</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0619928601642499</v>
+        <v>0.06307679987061918</v>
       </c>
       <c r="E12" t="n">
-        <v>45.67133331298828</v>
+        <v>40.8149299621582</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5020519835841313</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -863,23 +863,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.003890699474141002</v>
+        <v>0.004058550577610731</v>
       </c>
       <c r="C13" t="n">
-        <v>0.04843297973275185</v>
+        <v>0.05080628767609596</v>
       </c>
       <c r="D13" t="n">
-        <v>0.06237547173481738</v>
+        <v>0.0637067545681832</v>
       </c>
       <c r="E13" t="n">
-        <v>52.3447265625</v>
+        <v>42.19279479980469</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4952120383036936</v>
+        <v>0.5268817204301075</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -898,23 +898,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.004407931119203568</v>
+        <v>0.002946869703009725</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05449587851762772</v>
+        <v>0.04232752323150635</v>
       </c>
       <c r="D14" t="n">
-        <v>0.06639225195159122</v>
+        <v>0.05428507808790298</v>
       </c>
       <c r="E14" t="n">
-        <v>43.79434204101562</v>
+        <v>44.41254806518555</v>
       </c>
       <c r="F14" t="n">
-        <v>0.53077975376197</v>
+        <v>0.510752688172043</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01277330797165632</v>
+        <v>0.01168010663241148</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06014643609523773</v>
+        <v>0.05620387569069862</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1130190602140025</v>
+        <v>0.108074542018051</v>
       </c>
       <c r="E15" t="n">
-        <v>28.02482032775879</v>
+        <v>25.28511238098145</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5266757865937073</v>
+        <v>0.5228494623655914</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -968,23 +968,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.008468260988593102</v>
+        <v>0.005861027631908655</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05886462330818176</v>
+        <v>0.04935817793011665</v>
       </c>
       <c r="D16" t="n">
-        <v>0.09202315463291345</v>
+        <v>0.07655734864732879</v>
       </c>
       <c r="E16" t="n">
-        <v>22.57762336730957</v>
+        <v>24.58402442932129</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5376196990424077</v>
+        <v>0.5376344086021505</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1003,23 +1003,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.008310945704579353</v>
+        <v>0.01114773936569691</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0755494087934494</v>
+        <v>0.07284024357795715</v>
       </c>
       <c r="D17" t="n">
-        <v>0.09116438835740277</v>
+        <v>0.1055828554534159</v>
       </c>
       <c r="E17" t="n">
-        <v>52.2618293762207</v>
+        <v>26.70821571350098</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4678522571819426</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1038,23 +1038,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0108782984316349</v>
+        <v>0.006862477399408817</v>
       </c>
       <c r="C18" t="n">
-        <v>0.07880063354969025</v>
+        <v>0.07336050271987915</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1042990816432959</v>
+        <v>0.08284007121803323</v>
       </c>
       <c r="E18" t="n">
-        <v>62.25688552856445</v>
+        <v>64.76457977294922</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4979480164158687</v>
+        <v>0.4852150537634409</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1077,19 +1077,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.007164469308918342</v>
+        <v>0.006552868086146191</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05860261945053935</v>
+        <v>0.05554686300456524</v>
       </c>
       <c r="D19" t="n">
-        <v>0.08251714173437805</v>
+        <v>0.07885667943866712</v>
       </c>
       <c r="E19" t="n">
-        <v>41.92680358886719</v>
+        <v>36.79116058349609</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5046169630642955</v>
+        <v>0.5220094086021505</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
